--- a/Back_Expansion/Back_Expansion_Keypad_6/Release/PCBA/02.BOM/Bill_Of_Materials-BoM.xlsx
+++ b/Back_Expansion/Back_Expansion_Keypad_6/Release/PCBA/02.BOM/Bill_Of_Materials-BoM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JK\Desktop\src_moddo\moddoMOUSE-PCB\Back_Expansion\Back_Expansion_Keypad_12\Release\PCBA\02.BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JK\Desktop\src_moddo\moddoMOUSE-PCB\Back_Expansion\Back_Expansion_Keypad_6\Release\PCBA\02.BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE31E76-61CD-49EA-A427-218C95AE7B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51D75DE-057E-483A-B900-8E328844DA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9984" yWindow="-17388" windowWidth="41496" windowHeight="16776" xr2:uid="{3D9877AC-C528-47C5-B8E6-A3DE921EC85C}"/>
+    <workbookView xWindow="9984" yWindow="-17388" windowWidth="41496" windowHeight="16776" xr2:uid="{8B708A10-9277-4AC5-ADA9-919BDC7A06B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill_Of_Materials-BoM" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>Supplier Link</t>
   </si>
   <si>
-    <t>J1, J2</t>
+    <t>J1</t>
   </si>
   <si>
     <t>2328702-8</t>
@@ -92,7 +92,7 @@
     <t>https://www.digikey.ca/en/products/detail/te-connectivity-amp-connectors/2328702-8/9565576?s=N4IgTCBcDa4MxgBwHYAMYC0iQF0C%2BQA</t>
   </si>
   <si>
-    <t>SW0, SW1, SW2, SW3, SW4, SW5, SW6, SW7, SW8, SW9, SW10, SW11</t>
+    <t>SW0, SW1, SW2, SW3, SW4, SW5</t>
   </si>
   <si>
     <t>GT-TS090C-H031-L5</t>
@@ -503,7 +503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17849C57-B4DB-44DD-8AEA-F20A84B1D94C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F036C4F-6976-4163-B273-4BF9540D22EC}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -569,7 +569,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>7</v>
@@ -601,7 +601,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>7</v>
